--- a/public/credit_events.xlsx
+++ b/public/credit_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T169"/>
+  <dimension ref="A1:V169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,16 @@
           <t>auction_url</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>notes_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -599,6 +609,8 @@
           <t>https://www.cdsdeterminationscommittees.org/documents/2026/04/liberty-interactive-llc-bankruptcy-credit-event-4-21-26.pdf/</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -677,6 +689,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/sns-bank-nv/</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -765,6 +779,16 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/nfe-financing-llc/</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Americas DC Failure to Pay (Nov 2025) as New Fortress Energy missed term-loan interest and entered forbearance (rated SD by S&amp;P). Recent event — limited published DC commentary so far.</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2025-12-19/new-fortress-energy-s-delinquent-payments-mount-amid-debt-talks</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -851,6 +875,16 @@
       <c r="T5" t="inlineStr">
         <is>
           <t>https://www.cdsdeterminationscommittees.org/cds/ardagh-packaging-finance-plc-3/</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>EMEA DC split on timing and escalated to an External Review Panel, which ruled (15 Dec 2025) a Restructuring Credit Event occurred by 29 Sep 2025 — a landmark holding that a binding TSA + consent solicitation can trigger Restructuring before the deal is implemented. ~$3.5bn gross notional across ~1,100 contracts.</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>https://www.jonesday.com/en/insights/2025/12/important-guidance-on-restructuring-credit-event-triggers-under-isda-definitions</t>
         </is>
       </c>
     </row>
@@ -933,6 +967,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/new-fortress-energy-inc-2/</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1019,6 +1055,16 @@
       <c r="T7" t="inlineStr">
         <is>
           <t>https://www.cdsdeterminationscommittees.org/cds/intrum-ab/</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>EMEA DC ruled the 15 Nov 2024 US Chapter 11 filing a Bankruptcy Credit Event; contentious because bondholders disputed whether the debt collector was genuinely distressed (no obvious liquidity crisis). Auction settled at 76 (~24% payout, ~$90m).</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://news.bloomberglaw.com/bankruptcy-law/cds-panel-rules-intrums-bankruptcy-filing-is-a-credit-event</t>
         </is>
       </c>
     </row>
@@ -1101,6 +1147,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/avon-products-inc-2/</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1189,6 +1237,16 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/altice-france-s-a/</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bankruptcy Credit Event (accelerated safeguard, 27 May 2024). Took 22 DC meetings to settle: a 95% bond lock-up threatened to starve the auction of deliverables and skew the price — a flashpoint in the net-short / manufactured-default debate. Auction 87.75.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>https://www.ifre.com/topic-codes/2304255/cds-market-passes-altice-debt-test</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1277,6 +1335,16 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/atos-se/</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bankruptcy Credit Event (30 Jul 2024) on entry into accelerated safeguard — Europe's first CDS trigger since Casino. Auction 9 Oct 2024.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://www.9fin.com/insights/atos-credit-cds-trigger-casino</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1365,6 +1433,16 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/casino-guichard-perrachon-sa-11/</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>DC reversed itself repeatedly — no bankruptcy (5 Jun 2023) and twice no failure-to-pay (9 Jun, 7 Aug) citing waivers/conciliation — before finally declaring a Failure to Pay on 6 Sep 2023 once the 30-day grace period lapsed.</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://www.nasdaq.com/articles/cds-panel-rules-no-failure-to-pay-credit-event-occurred-at-casino</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1453,6 +1531,16 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/diamond-sports-group-llc/</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Americas DC: Bankruptcy Credit Event on the Mar 2023 Chapter 11 of the Sinclair-spun regional sports networks; the group later sued parent Sinclair over ~$1.5bn of alleged misallocation. Auction 13 Apr 2023.</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://www.sportico.com/business/media/2024/diamond-sports-group-bankruptcy-timeline-1234715961/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1537,6 +1625,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/rite-aid-corporation/</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1607,6 +1697,16 @@
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sovereign Restructuring Credit Event (19 Aug 2022) after creditors backed a two-year freeze on ~$20bn of debt amid the war; auction 28 Sep 2022. (Ukraine also had a 2015 Repudiation/Moratorium event.)</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://money.usnews.com/investing/news/articles/2022-08-19/ukraines-sovereign-debt-freeze-to-trigger-cds-payments</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1695,6 +1795,16 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/vue-international-bidco-plc/</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>EMEA DC ruled Vue's debt-for-equity swap a Restructuring Credit Event (12 of 13 members in favour, 22 Mar 2023); the parallel Bankruptcy question was left open. ~$807m gross / $62m net.</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://news.bloomberglaw.com/capital-markets/swaps-panel-rules-vues-debt-overhaul-is-a-restructuring-event</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1779,6 +1889,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/talen-energy-supply-llc/</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1833,6 +1945,16 @@
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>First sovereign trigger of the war: EMEA DC found a Failure to Pay (2022), but OFAC sanctions blocked settlement until US Treasury General License 46 authorised a bespoke auction process (settled Sep 2022).</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://www.alston.com/en/insights/publications/2022/07/russian-bond-default-and-cds-credit-event</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1891,6 +2013,16 @@
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>First sovereign trigger of the war: EMEA DC found a Failure to Pay (2022), but OFAC sanctions blocked settlement until US Treasury General License 46 authorised a bespoke auction process (settled Sep 2022).</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://www.alston.com/en/insights/publications/2022/07/russian-bond-default-and-cds-credit-event</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1977,6 +2109,16 @@
       <c r="T19" t="inlineStr">
         <is>
           <t>https://www.cdsdeterminationscommittees.org/cds/the-russian-federation-3/</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>First sovereign trigger of the war: EMEA DC found a Failure to Pay (2022), but OFAC sanctions blocked settlement until US Treasury General License 46 authorised a bespoke auction process (settled Sep 2022).</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://www.alston.com/en/insights/publications/2022/07/russian-bond-default-and-cds-credit-event</t>
         </is>
       </c>
     </row>
@@ -2037,6 +2179,16 @@
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>First sovereign trigger of the war: EMEA DC found a Failure to Pay (2022), but OFAC sanctions blocked settlement until US Treasury General License 46 authorised a bespoke auction process (settled Sep 2022).</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://www.alston.com/en/insights/publications/2022/07/russian-bond-default-and-cds-credit-event</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2125,6 +2277,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/selecta-group-b-v/</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2213,6 +2367,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/pizzaexpress-financing-1-plc/</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2301,6 +2457,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/matalan-finance-plc/</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2389,6 +2547,16 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/wirecard-ag/</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bankruptcy Credit Event (Jul 2020) after the €1.9bn accounting-fraud collapse; the DC acted on the insolvency-filing announcement, though fraud claims complicated recovery. Funds paid ~$208m.</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://news.bloomberglaw.com/bankruptcy-law/cds-committee-rules-wirecard-swaps-in-bankruptcy-credit-event</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2477,6 +2645,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/argentine-republic/</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2565,6 +2735,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/the-hertz-corporation/</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2653,6 +2825,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/intelsat-investments-s-a/</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2737,6 +2911,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/neiman-marcus-group-llc/</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2821,6 +2997,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/j-c-penney-company-inc/</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2905,6 +3083,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/diamond-offshore-drilling-inc/</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2989,6 +3169,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/republic-of-ecuador/</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3077,6 +3259,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/frontier-communications-corporation/</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3161,6 +3345,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/whiting-petroleum-corporation/</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3249,6 +3435,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/the-lebanese-republic/</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3333,6 +3521,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/the-mcclatchy-company/</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3417,6 +3607,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/noble-corporation-plc/</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3501,6 +3693,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/europcar-mobility-group-s-a/</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3589,6 +3783,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/chesapeake-energy-corporation/</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3647,6 +3843,16 @@
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bankruptcy Credit Event on the 23 Sep 2019 compulsory liquidation; notable for the CDS roll-date wrinkle (contracts expiring 20 Sep missed the trigger) and for hedge funds' CDS incentives complicating the failed rescue.</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>https://www.kramerlevin.com/en/perspectives-search/thomas-cook-cds-when-does-a-corporate-debt-reorganization-amount-to-a-bankruptcy-credit-event</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3707,6 +3913,16 @@
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bankruptcy Credit Event on the 23 Sep 2019 compulsory liquidation; notable for the CDS roll-date wrinkle (contracts expiring 20 Sep missed the trigger) and for hedge funds' CDS incentives complicating the failed rescue.</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>https://www.kramerlevin.com/en/perspectives-search/thomas-cook-cds-when-does-a-corporate-debt-reorganization-amount-to-a-bankruptcy-credit-event</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3795,6 +4011,16 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/thomas-cook-group-plc/</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bankruptcy Credit Event on the 23 Sep 2019 compulsory liquidation; notable for the CDS roll-date wrinkle (contracts expiring 20 Sep missed the trigger) and for hedge funds' CDS incentives complicating the failed rescue.</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>https://www.kramerlevin.com/en/perspectives-search/thomas-cook-cds-when-does-a-corporate-debt-reorganization-amount-to-a-bankruptcy-credit-event</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3883,6 +4109,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/hema-bondco-i-b-v/</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3971,6 +4199,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/top-gun-realisations-61-limited/</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4059,6 +4289,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/california-resources-corporation/</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4143,6 +4375,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/weatherford-international-ltd-2/</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4231,6 +4465,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/rallye/</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4319,6 +4555,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/new-look-senior-issuer-plc-3/</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4403,6 +4641,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/windstream-services-llc-6/</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4487,6 +4727,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/dean-foods-company/</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4575,6 +4817,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/steinhoff-europe-ag/</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4641,6 +4885,8 @@
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4729,6 +4975,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/parker-drilling-company/</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4817,6 +5065,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/astaldi-spa-2/</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4905,6 +5155,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/galapagos-holding-sa/</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4993,6 +5245,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/sears-roebuck-acceptance-corp/</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5081,6 +5335,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/nine-west-holdings-inc/</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5141,6 +5397,8 @@
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5229,6 +5487,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/noble-group-limited-4/</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5317,6 +5577,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/petroleos-de-venezuela-s-a-3/</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5371,6 +5633,8 @@
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5459,6 +5723,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/toys-to-toys-r-us-delaware-inc-lcds-credit-event/</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5513,6 +5779,8 @@
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5567,6 +5835,8 @@
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5655,6 +5925,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/banca-monte-dei-paschi-di-siena-s-p-a/</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5743,6 +6015,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/puerto-rico-electric-power-authority-prepa/</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5831,6 +6105,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/genon-energy-inc/</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5917,6 +6193,16 @@
       <c r="T67" t="inlineStr">
         <is>
           <t>https://www.cdsdeterminationscommittees.org/cds/usp97475an08/</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Failure to Pay for both the sovereign and PDVSA (16 Nov 2017, unanimous 15-firm DC); US sanctions (EO 13808) forced ISDA to publish a special Venezuela Protocol carving out 'restricted' debt so an auction could still function.</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/protocol/isda-2017-venezuela-additional-provisions-protocol/</t>
         </is>
       </c>
     </row>
@@ -5977,6 +6263,16 @@
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Novel intercompany / 'orphaned' event: Americas DC voted 15-0 (Dec 2016) that iHeart's election not to repay $57m of notes held by its own subsidiary was a Failure to Pay, despite arguments the payment wasn't really 'due'. ~$154m settled.</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>https://www.lexology.com/library/detail.aspx?g=adac8169-f5e4-41ed-a078-74f2733fd645</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6035,6 +6331,16 @@
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Novel intercompany / 'orphaned' event: Americas DC voted 15-0 (Dec 2016) that iHeart's election not to repay $57m of notes held by its own subsidiary was a Failure to Pay, despite arguments the payment wasn't really 'due'. ~$154m settled.</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>https://www.lexology.com/library/detail.aspx?g=adac8169-f5e4-41ed-a078-74f2733fd645</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6093,6 +6399,16 @@
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Novel intercompany / 'orphaned' event: Americas DC voted 15-0 (Dec 2016) that iHeart's election not to repay $57m of notes held by its own subsidiary was a Failure to Pay, despite arguments the payment wasn't really 'due'. ~$154m settled.</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>https://www.lexology.com/library/detail.aspx?g=adac8169-f5e4-41ed-a078-74f2733fd645</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6177,6 +6493,16 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/iheart-communications-inc-lcds-credit-event/</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Novel intercompany / 'orphaned' event: Americas DC voted 15-0 (Dec 2016) that iHeart's election not to repay $57m of notes held by its own subsidiary was a Failure to Pay, despite arguments the payment wasn't really 'due'. ~$154m settled.</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>https://www.lexology.com/library/detail.aspx?g=adac8169-f5e4-41ed-a078-74f2733fd645</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6263,6 +6589,16 @@
       <c r="T72" t="inlineStr">
         <is>
           <t>https://www.cdsdeterminationscommittees.org/lcds/iheart-communications-inc-lcds-credit-event/</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Novel intercompany / 'orphaned' event: Americas DC voted 15-0 (Dec 2016) that iHeart's election not to repay $57m of notes held by its own subsidiary was a Failure to Pay, despite arguments the payment wasn't really 'due'. ~$154m settled.</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>https://www.lexology.com/library/detail.aspx?g=adac8169-f5e4-41ed-a078-74f2733fd645</t>
         </is>
       </c>
     </row>
@@ -6319,6 +6655,8 @@
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6407,6 +6745,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/grupo-isolux-corsan-finance-b-v/</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6461,6 +6801,8 @@
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6549,6 +6891,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/commonwealth-of-puerto-rico/</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6637,6 +6981,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/portugal-telecom-international-finance-b-v/</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6691,6 +7037,8 @@
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6779,6 +7127,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/norske-skogsindustrier-asa/</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6867,6 +7217,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/peabody-energy-corporation/</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6955,6 +7307,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/pacific-exploration-production-corporation/</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7043,6 +7397,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/alpha-appalachia-holdings-inc-fka-massey-energy-company/</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7131,6 +7487,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/sabine-oil-gas-corporation/</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7215,6 +7573,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/caesars-entertainment-operating-company-inc-lcds-credit-event/</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7295,6 +7655,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/pages-jaunes-credit-event-2/</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7355,6 +7717,16 @@
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>BES's Aug-2014 resolution split it into a good bank (Novo Banco) and bad bank; ISDA ruled a succession transferring CDS to Novo Banco, then the 2015 bond retransfer stranded protection buyers (see Novo Banco).</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/marketintelligence/en/mi/research-analysis/08082014120606Banco-Espirito-Santo-creates-a-CDS-orphan.html</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7443,6 +7815,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/argentine-republic/</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7519,6 +7893,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=AIFUL</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7573,6 +7949,16 @@
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Failure to Pay (30 Jul 2014) after Judge Griesa's pari passu injunction blocked payment to exchange bondholders unless holdouts were paid — a 'won't-pay vs can't-pay' selective default. Auction settled at 39.5. (Argentina also had a separate 2020 restructuring.)</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/2014/09/03/isda-americas-credit-derivatives-determinations-committee-cds-auction-relating-to-the-argentine-republic/</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7661,6 +8047,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/energy-future-holdings-corp-4/</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7749,6 +8137,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/energy-future-intermediate-holding-company-llc/</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7837,6 +8227,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/texas-competitive-electric-holdings-company-llc-2/</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7925,6 +8317,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/ogx-petroleo-e-gas-participacoes-s-a/</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8013,6 +8407,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/cds/codere-finance-luxembourg-sa/</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8097,6 +8493,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/cengage-learning-acquisitions-inc-lcds-credit-event/</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8185,6 +8583,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/urbi-desarrollos-urbanos-s-a-b-de-c-v/</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8265,6 +8665,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/lcds/supermedia-inc-dex-media-west-inc-lcds-credit-event/</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8345,6 +8747,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/supermedia-inc-dex-media-west-inc-lcds-credit-event/</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8399,6 +8803,16 @@
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Restructuring Credit Event (Feb 2013) after the Dutch state expropriated SNS Reaal's subordinated debt; with the sub bonds expropriated there were none to auction, so settlement ran on senior bonds — a gap that drove the new 2014 Governmental Intervention trigger.</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/2013/02/13/isda-emea-credit-derivatives-determinations-committee-sns-bank-restructuring-credit-event/</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8487,6 +8901,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/sns-bank-nv/</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8575,6 +8991,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/edison-mission-energy/</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8663,6 +9081,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/overseas-shipholding-group-inc/</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8751,6 +9171,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/houghton-mifflin-harcourt-publishing-company/</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8839,6 +9261,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/residential-capital-llc/</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8923,6 +9347,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/hawker-beechcraft-acquisition-co-llc/</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8989,6 +9415,8 @@
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9073,6 +9501,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/financier-gaillon-7/</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9161,6 +9591,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/the-hellenic-republic-3/</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9249,6 +9681,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/elpida-memory-inc/</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9337,6 +9771,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/eastman-kodak-company/</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9425,6 +9861,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/northern-rock-asset-management-plc/</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9513,6 +9951,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/amr-corporation/</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9601,6 +10041,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/the-pmi-group-inc/</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9681,6 +10123,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Panrico-A06</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9769,6 +10213,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/dynegy-holdings-llc/</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9857,6 +10303,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/seat-paginegialle-s-p-a-2/</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9945,6 +10393,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/victor-company-of-japan-limited/</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10033,6 +10483,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/the-governor-and-company-of-the-bank-of-ireland/</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10121,6 +10573,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/irish-life-permanent-plc/</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10205,6 +10659,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/allied-irish-banks-plc-3/</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10289,6 +10745,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/takefuji-corporation/</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10377,6 +10835,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/anglo-irish-bank-corporation-limited/</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10465,6 +10925,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/ambac-financial-group-inc/</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10549,6 +11011,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/truvo-subsidiary-corp/</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10633,6 +11097,8 @@
           <t>https://www.cdsdeterminationscommittees.org/cds/ambac-assurance-corporation/</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10715,6 +11181,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=HELLAS-II</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
@@ -10779,6 +11247,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ABY</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
@@ -10853,6 +11323,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/avaya-inc-lcds-credit-event/</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
@@ -10923,6 +11395,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/boston-generating-llc/</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
@@ -10987,6 +11461,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BOW</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
@@ -11051,6 +11527,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BRADBI</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -11115,6 +11593,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CAPFIN</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
@@ -11179,6 +11659,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEMSAB</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
@@ -11243,6 +11725,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Holdings</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
@@ -11307,6 +11791,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Operating</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
@@ -11371,6 +11857,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEM</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
@@ -11435,6 +11923,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CIT</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
@@ -11499,6 +11989,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXME</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
@@ -11563,6 +12055,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXMW</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
@@ -11627,6 +12121,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Edscha-A05</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -11691,6 +12187,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Eircom-A06</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
@@ -11755,6 +12253,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=FGIC</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
@@ -11819,6 +12319,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGP</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
@@ -11883,6 +12385,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GM</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -11947,6 +12451,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGC</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
@@ -12011,6 +12517,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GLK</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
@@ -12075,6 +12583,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=HAZ-HOC</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
@@ -12139,6 +12649,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=IAR</t>
         </is>
       </c>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
@@ -12203,6 +12715,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=JALC</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
@@ -12267,6 +12781,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BTAB</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
@@ -12331,6 +12847,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ALLBNK</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -12395,6 +12913,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=LEA</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
@@ -12459,6 +12979,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=AIND-LYON</t>
         </is>
       </c>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
@@ -12523,6 +13045,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=McCarthy-A06</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
@@ -12593,6 +13117,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=MEDIANA</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
@@ -12657,6 +13183,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=MGM</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
@@ -12721,6 +13249,16 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=NAFT</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Sovereign Restructuring Credit Event (19 Aug 2022) after creditors backed a two-year freeze on ~$20bn of debt amid the war; auction 28 Sep 2022. (Ukraine also had a 2015 Repudiation/Moratorium event.)</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>https://money.usnews.com/investing/news/articles/2022-08-19/ukraines-sovereign-debt-freeze-to-trigger-cds-payments</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
@@ -12785,6 +13323,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PCG-PacGas+Elec</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
@@ -12849,6 +13389,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
@@ -12913,6 +13455,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD-Inc</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
@@ -12977,6 +13521,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS-SFTP</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -13041,6 +13587,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
@@ -13105,6 +13653,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SSPFIN</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
@@ -13169,6 +13719,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SYNHL-Gua</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -13233,6 +13785,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGP-RSELP</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
@@ -13297,6 +13851,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=TMMFP</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -13371,6 +13927,8 @@
           <t>https://www.cdsdeterminationscommittees.org/lcds/truvo-usa-llc-credit-event/</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -13435,6 +13993,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=VC</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -13505,6 +14065,8 @@
           <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=YELLLN-LTD</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/credit_events.xlsx
+++ b/public/credit_events.xlsx
@@ -10665,22 +10665,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2011-04-14</t>
+          <t>2010-11-23</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Takefuji Corporation</t>
+          <t>ANGLO IRISH BANK CORPORATION LIMITED</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Restructuring</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -10692,42 +10692,46 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>9000</v>
+        <v>9002</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2010092801</t>
+          <t>2010122201</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2010-10-28</t>
+          <t>2011-02-02</t>
         </is>
       </c>
       <c r="L121" t="b">
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="N121" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
       <c r="O121" t="n">
-        <v>-168</v>
+        <v>71</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Subordinated - B3</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>TAKFUJ</t>
+          <t>ANGBKL</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10737,12 +10741,12 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/takefuji-corporation/</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/anglo-irish-bank-corporation-limited-credit-event-december-restructuring/</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/takefuji-corporation/</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/anglo-irish-bank-corporation-limited/</t>
         </is>
       </c>
       <c r="U121" t="inlineStr"/>
@@ -10751,22 +10755,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2010-11-23</t>
+          <t>2010-11-09</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ANGLO IRISH BANK CORPORATION LIMITED</t>
+          <t>Ambac Financial Group, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Americas</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Restructuring</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -10778,46 +10782,46 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>9002</v>
+        <v>9001</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2010122201</t>
+          <t>2010110901</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2011-02-02</t>
+          <t>2010-12-10</t>
         </is>
       </c>
       <c r="L122" t="b">
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>18</v>
+        <v>9.5</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Subordinated - B3</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>ANGBKL</t>
+          <t>ABK</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10827,12 +10831,12 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/anglo-irish-bank-corporation-limited-credit-event-december-restructuring/</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/ambac-financial-group-inc/</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/anglo-irish-bank-corporation-limited/</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/ambac-financial-group-inc/</t>
         </is>
       </c>
       <c r="U122" t="inlineStr"/>
@@ -10841,17 +10845,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2010-11-09</t>
+          <t>2010-06-29</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ambac Financial Group, Inc.</t>
+          <t>TRUVO SUBSIDIARY CORP.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10868,37 +10872,33 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>9001</v>
+        <v>3000</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2010110901</t>
+          <t>2010070101</t>
         </is>
       </c>
       <c r="I123" t="n">
         <v>1</v>
       </c>
       <c r="J123" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2010-12-10</t>
+          <t>2010-07-15</t>
         </is>
       </c>
       <c r="L123" t="b">
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>ABK</t>
+          <t>TRUVO-SubCo</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/ambac-financial-group-inc/</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/truvo-subsidiary-corp/</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/ambac-financial-group-inc/</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/truvo-subsidiary-corp/</t>
         </is>
       </c>
       <c r="U123" t="inlineStr"/>
@@ -10931,17 +10931,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2010-06-29</t>
+          <t>2010-03-26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TRUVO SUBSIDIARY CORP.</t>
+          <t>Ambac Assurance Corporation</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Americas</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10958,33 +10958,33 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2010070101</t>
+          <t>2010032501</t>
         </is>
       </c>
       <c r="I124" t="n">
         <v>1</v>
       </c>
       <c r="J124" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
+          <t>2010-06-04</t>
         </is>
       </c>
       <c r="L124" t="b">
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>TRUVO-SubCo</t>
+          <t>ABK-AssurCorp</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/truvo-subsidiary-corp/</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/ambac-assurance-corporation/</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/truvo-subsidiary-corp/</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/ambac-assurance-corporation/</t>
         </is>
       </c>
       <c r="U124" t="inlineStr"/>
@@ -11017,17 +11017,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2010-03-26</t>
+          <t>2009-12-09</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ambac Assurance Corporation</t>
+          <t>Hellas Telecommunications (Luxembourg) II</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11040,145 +11040,125 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>DC credit event determination (auction held)</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
-        <v>4000</v>
-      </c>
+          <t>Determination published</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2010032501</t>
+          <t>2009111801</t>
         </is>
       </c>
       <c r="I125" t="n">
         <v>1</v>
       </c>
       <c r="J125" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2010-06-04</t>
+          <t>2009-12-15</t>
         </is>
       </c>
       <c r="L125" t="b">
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>20</v>
+        <v>1.375</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Subordinated</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>ABK-AssurCorp</t>
+          <t>HELLAS-II</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>dc-isda</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/ambac-assurance-corporation/</t>
+          <t>https://www.cdsdeterminationscommittees.org/docs/EMEA_Determinations_Committee_Decision_2009091203.pdf</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/cds/ambac-assurance-corporation/</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=HELLAS-II</t>
         </is>
       </c>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2009-12-09</t>
-        </is>
-      </c>
+      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Hellas Telecommunications (Luxembourg) II</t>
+          <t>ABITIBI-CONSOLIDATED INC.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Bankruptcy</t>
-        </is>
-      </c>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="b">
         <v>1</v>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Determination published</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>2009111801</t>
-        </is>
-      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2009-12-15</t>
+          <t>2009-04-17</t>
         </is>
       </c>
       <c r="L126" t="b">
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>1.375</v>
+        <v>3.25</v>
       </c>
       <c r="N126" t="inlineStr"/>
-      <c r="O126" t="n">
-        <v>6</v>
-      </c>
+      <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Subordinated</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>HELLAS-II</t>
+          <t>ABY</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>creditfixings</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/docs/EMEA_Determinations_Committee_Decision_2009091203.pdf</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ABY</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=HELLAS-II</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ABY</t>
         </is>
       </c>
       <c r="U126" t="inlineStr"/>
@@ -11188,63 +11168,73 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ABITIBI-CONSOLIDATED INC.</t>
+          <t>Avaya Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Americas</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="b">
         <v>1</v>
       </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>DC credit event determination (auction held)</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>9096</v>
+      </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2009-04-17</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="L127" t="b">
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N127" t="inlineStr"/>
+        <v>80.5</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Lien1</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ABY</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>creditfixings</t>
+          <t>dc-isda</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ABY</t>
+          <t>https://www.cdsdeterminationscommittees.org/lcds/avaya-inc-lcds-credit-event/</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ABY</t>
+          <t>https://www.cdsdeterminationscommittees.org/lcds/avaya-inc-lcds-credit-event/</t>
         </is>
       </c>
       <c r="U127" t="inlineStr"/>
@@ -11254,7 +11244,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Avaya Inc.</t>
+          <t>Boston Generating, LLC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -11272,7 +11262,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>9096</v>
+        <v>8000</v>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
@@ -11283,29 +11273,25 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2010-09-21</t>
         </is>
       </c>
       <c r="L128" t="b">
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+        <v>96.75</v>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lien1</t>
+          <t>Lien 1</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>BOSG</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11315,12 +11301,12 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/lcds/avaya-inc-lcds-credit-event/</t>
+          <t>https://www.cdsdeterminationscommittees.org/lcds/boston-generating-llc/</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/lcds/avaya-inc-lcds-credit-event/</t>
+          <t>https://www.cdsdeterminationscommittees.org/lcds/boston-generating-llc/</t>
         </is>
       </c>
       <c r="U128" t="inlineStr"/>
@@ -11330,69 +11316,63 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Boston Generating, LLC</t>
+          <t>Bowater Incorporated</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="b">
         <v>1</v>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>DC credit event determination (auction held)</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>8000</v>
-      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2010-09-21</t>
+          <t>2009-05-12</t>
         </is>
       </c>
       <c r="L129" t="b">
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>96.75</v>
+        <v>15</v>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lien 1</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>BOSG</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>dc-isda</t>
+          <t>creditfixings</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/lcds/boston-generating-llc/</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BOW</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/lcds/boston-generating-llc/</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BOW</t>
         </is>
       </c>
       <c r="U129" t="inlineStr"/>
@@ -11402,7 +11382,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bowater Incorporated</t>
+          <t>Bradford &amp; Bingley PLC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -11425,14 +11405,14 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2009-05-12</t>
+          <t>2009-07-30</t>
         </is>
       </c>
       <c r="L130" t="b">
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>15</v>
+        <v>94.625</v>
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
@@ -11443,7 +11423,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BRADBI</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11453,12 +11433,12 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BOW</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BRADBI</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BOW</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BRADBI</t>
         </is>
       </c>
       <c r="U130" t="inlineStr"/>
@@ -11468,7 +11448,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bradford &amp; Bingley PLC</t>
+          <t>Capmark Financial Group Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -11491,14 +11471,14 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2009-07-30</t>
+          <t>2009-04-22</t>
         </is>
       </c>
       <c r="L131" t="b">
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>94.625</v>
+        <v>23.375</v>
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
@@ -11509,7 +11489,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>BRADBI</t>
+          <t>CAPFIN</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11519,12 +11499,12 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BRADBI</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CAPFIN</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BRADBI</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CAPFIN</t>
         </is>
       </c>
       <c r="U131" t="inlineStr"/>
@@ -11534,7 +11514,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Capmark Financial Group Inc.</t>
+          <t>Cemex S.A.B. de C.V.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -11557,14 +11537,14 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2009-04-22</t>
+          <t>2010-02-18</t>
         </is>
       </c>
       <c r="L132" t="b">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>23.375</v>
+        <v>97</v>
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
@@ -11575,7 +11555,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>CAPFIN</t>
+          <t>CEMSAB</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11585,12 +11565,12 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CAPFIN</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEMSAB</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CAPFIN</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEMSAB</t>
         </is>
       </c>
       <c r="U132" t="inlineStr"/>
@@ -11600,7 +11580,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cemex S.A.B. de C.V.</t>
+          <t>CHARTER COMMUNICATIONS HOLDINGS, LLC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -11623,14 +11603,14 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2010-02-18</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="L133" t="b">
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>97</v>
+        <v>2.375</v>
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
@@ -11641,7 +11621,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>CEMSAB</t>
+          <t>CHTR-Holdings</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11651,12 +11631,12 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEMSAB</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Holdings</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEMSAB</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Holdings</t>
         </is>
       </c>
       <c r="U133" t="inlineStr"/>
@@ -11666,7 +11646,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CHARTER COMMUNICATIONS HOLDINGS, LLC</t>
+          <t>Charter Communications Operating, LLC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -11696,18 +11676,18 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>2.375</v>
+        <v>78</v>
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Lien 1</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>CHTR-Holdings</t>
+          <t>CHTR-Operating</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11717,12 +11697,12 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Holdings</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Operating</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Holdings</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Operating</t>
         </is>
       </c>
       <c r="U134" t="inlineStr"/>
@@ -11732,7 +11712,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Charter Communications Operating, LLC</t>
+          <t>Chemtura Corporation</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -11755,25 +11735,25 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2009-04-21</t>
+          <t>2009-04-14</t>
         </is>
       </c>
       <c r="L135" t="b">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lien 1</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>CHTR-Operating</t>
+          <t>CEM</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11783,12 +11763,12 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Operating</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEM</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CHTR-Operating</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEM</t>
         </is>
       </c>
       <c r="U135" t="inlineStr"/>
@@ -11798,7 +11778,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Chemtura Corporation</t>
+          <t>CIT Group Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -11821,14 +11801,14 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2009-04-14</t>
+          <t>2009-11-20</t>
         </is>
       </c>
       <c r="L136" t="b">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>15</v>
+        <v>68.125</v>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
@@ -11839,7 +11819,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>CEM</t>
+          <t>CIT</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -11849,12 +11829,12 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEM</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CIT</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CEM</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CIT</t>
         </is>
       </c>
       <c r="U136" t="inlineStr"/>
@@ -11864,7 +11844,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CIT Group Inc.</t>
+          <t>Dex Media East LLC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -11887,25 +11867,25 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2009-11-20</t>
+          <t>2009-06-24</t>
         </is>
       </c>
       <c r="L137" t="b">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>68.125</v>
+        <v>77.25</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Lien 1</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>CIT</t>
+          <t>DXME</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -11915,12 +11895,12 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CIT</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXME</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=CIT</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXME</t>
         </is>
       </c>
       <c r="U137" t="inlineStr"/>
@@ -11930,7 +11910,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dex Media East LLC</t>
+          <t>DEX MEDIA WEST LLC</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -11960,7 +11940,7 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>77.25</v>
+        <v>82.875</v>
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
@@ -11971,7 +11951,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>DXME</t>
+          <t>DXMW</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -11981,12 +11961,12 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXME</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXMW</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXME</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXMW</t>
         </is>
       </c>
       <c r="U138" t="inlineStr"/>
@@ -11996,7 +11976,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DEX MEDIA WEST LLC</t>
+          <t>Edscha AG</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -12019,25 +11999,25 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2009-06-24</t>
+          <t>2009-05-28</t>
         </is>
       </c>
       <c r="L139" t="b">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>82.875</v>
+        <v>3.75</v>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lien 1</t>
+          <t>Lien 3</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>DXMW</t>
+          <t>Edscha-A05</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12047,12 +12027,12 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXMW</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Edscha-A05</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=DXMW</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Edscha-A05</t>
         </is>
       </c>
       <c r="U139" t="inlineStr"/>
@@ -12062,7 +12042,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edscha AG</t>
+          <t>Eircom- Credit Agreement (LevXCA2Y257H)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -12085,25 +12065,25 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2009-05-28</t>
+          <t>2012-05-02</t>
         </is>
       </c>
       <c r="L140" t="b">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>3.75</v>
+        <v>7.125</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lien 3</t>
+          <t>Lien 2</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Edscha-A05</t>
+          <t>Eircom-A06</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12113,12 +12093,12 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Edscha-A05</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Eircom-A06</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Edscha-A05</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Eircom-A06</t>
         </is>
       </c>
       <c r="U140" t="inlineStr"/>
@@ -12128,7 +12108,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Eircom- Credit Agreement (LevXCA2Y257H)</t>
+          <t>Financial Guaranty Insurance Company</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -12151,25 +12131,25 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2012-05-02</t>
+          <t>2010-01-07</t>
         </is>
       </c>
       <c r="L141" t="b">
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>7.125</v>
+        <v>26</v>
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Lien 2</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Eircom-A06</t>
+          <t>FGIC</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12179,12 +12159,12 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Eircom-A06</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=FGIC</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=Eircom-A06</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=FGIC</t>
         </is>
       </c>
       <c r="U141" t="inlineStr"/>
@@ -12194,7 +12174,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Guaranty Insurance Company</t>
+          <t>General Growth Properties, Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -12217,25 +12197,25 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2010-01-07</t>
+          <t>2009-05-13</t>
         </is>
       </c>
       <c r="L142" t="b">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>26</v>
+        <v>44.25</v>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Lien 1</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>FGIC</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12245,12 +12225,12 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=FGIC</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGP</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=FGIC</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGP</t>
         </is>
       </c>
       <c r="U142" t="inlineStr"/>
@@ -12260,7 +12240,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>General Growth Properties, Inc.</t>
+          <t>GENERAL MOTORS CORPORATION</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -12283,25 +12263,25 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2009-05-13</t>
+          <t>2009-06-12</t>
         </is>
       </c>
       <c r="L143" t="b">
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>44.25</v>
+        <v>12.5</v>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lien 1</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12311,12 +12291,12 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGP</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GM</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGP</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GM</t>
         </is>
       </c>
       <c r="U143" t="inlineStr"/>
@@ -12326,7 +12306,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GENERAL MOTORS CORPORATION</t>
+          <t>Georgia Gulf Corporation</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -12349,25 +12329,25 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2009-06-12</t>
+          <t>2009-06-10</t>
         </is>
       </c>
       <c r="L144" t="b">
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>12.5</v>
+        <v>83</v>
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Lien 1</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>GGC</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12377,12 +12357,12 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GM</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGC</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GM</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGC</t>
         </is>
       </c>
       <c r="U144" t="inlineStr"/>
@@ -12392,7 +12372,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Georgia Gulf Corporation</t>
+          <t>Great Lakes Chemical Corporation</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -12415,25 +12395,25 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2009-06-10</t>
+          <t>2009-04-14</t>
         </is>
       </c>
       <c r="L145" t="b">
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>83</v>
+        <v>18.25</v>
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Lien 1</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>GGC</t>
+          <t>GLK</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12443,12 +12423,12 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGC</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GLK</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GGC</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GLK</t>
         </is>
       </c>
       <c r="U145" t="inlineStr"/>
@@ -12458,7 +12438,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Great Lakes Chemical Corporation</t>
+          <t>HLI Operating Company, Inc.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -12481,25 +12461,25 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2009-04-14</t>
+          <t>2009-06-09</t>
         </is>
       </c>
       <c r="L146" t="b">
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>18.25</v>
+        <v>9.5</v>
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Lien 1</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>GLK</t>
+          <t>HAZ-HOC</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12509,12 +12489,12 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GLK</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=HAZ-HOC</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=GLK</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=HAZ-HOC</t>
         </is>
       </c>
       <c r="U146" t="inlineStr"/>
@@ -12524,7 +12504,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HLI Operating Company, Inc.</t>
+          <t>Idearc Inc.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -12547,14 +12527,14 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2009-06-09</t>
+          <t>2009-04-23</t>
         </is>
       </c>
       <c r="L147" t="b">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>9.5</v>
+        <v>38.5</v>
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
@@ -12565,7 +12545,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>HAZ-HOC</t>
+          <t>IAR</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -12575,12 +12555,12 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=HAZ-HOC</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=IAR</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=HAZ-HOC</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=IAR</t>
         </is>
       </c>
       <c r="U147" t="inlineStr"/>
@@ -12590,12 +12570,12 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Idearc Inc.</t>
+          <t>Japan Airlines Corporation</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -12613,25 +12593,25 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2009-04-23</t>
+          <t>2010-04-22</t>
         </is>
       </c>
       <c r="L148" t="b">
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>38.5</v>
+        <v>20</v>
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lien 1</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>IAR</t>
+          <t>JALC</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -12641,12 +12621,12 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=IAR</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=JALC</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=IAR</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=JALC</t>
         </is>
       </c>
       <c r="U148" t="inlineStr"/>
@@ -12656,12 +12636,12 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Japan Airlines Corporation</t>
+          <t>Joint Stock Company "BTA Bank"</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -12679,14 +12659,14 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2010-04-22</t>
+          <t>2009-06-10</t>
         </is>
       </c>
       <c r="L149" t="b">
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>20</v>
+        <v>10.25</v>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
@@ -12697,7 +12677,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>JALC</t>
+          <t>BTAB</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -12707,12 +12687,12 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=JALC</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BTAB</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=JALC</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BTAB</t>
         </is>
       </c>
       <c r="U149" t="inlineStr"/>
@@ -12722,7 +12702,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Joint Stock Company "BTA Bank"</t>
+          <t>JSC "Alliance Bank"</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -12745,14 +12725,14 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2009-06-10</t>
+          <t>2009-06-18</t>
         </is>
       </c>
       <c r="L150" t="b">
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>10.25</v>
+        <v>16.75</v>
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
@@ -12763,7 +12743,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>BTAB</t>
+          <t>ALLBNK</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -12773,12 +12753,12 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BTAB</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ALLBNK</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=BTAB</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ALLBNK</t>
         </is>
       </c>
       <c r="U150" t="inlineStr"/>
@@ -12788,7 +12768,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JSC "Alliance Bank"</t>
+          <t>Lear Corporation</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -12811,14 +12791,14 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2009-06-18</t>
+          <t>2009-07-21</t>
         </is>
       </c>
       <c r="L151" t="b">
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>16.75</v>
+        <v>38.5</v>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
@@ -12829,7 +12809,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>ALLBNK</t>
+          <t>LEA</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -12839,12 +12819,12 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ALLBNK</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=LEA</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=ALLBNK</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=LEA</t>
         </is>
       </c>
       <c r="U151" t="inlineStr"/>
@@ -12854,7 +12834,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lear Corporation</t>
+          <t>LyondellBasell Industries AF S.C.A.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -12877,14 +12857,14 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2009-07-21</t>
+          <t>2009-04-16</t>
         </is>
       </c>
       <c r="L152" t="b">
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>38.5</v>
+        <v>2</v>
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
@@ -12895,7 +12875,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>LEA</t>
+          <t>AIND-LYON</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -12905,12 +12885,12 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=LEA</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=AIND-LYON</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=LEA</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=AIND-LYON</t>
         </is>
       </c>
       <c r="U152" t="inlineStr"/>
@@ -12920,7 +12900,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LyondellBasell Industries AF S.C.A.</t>
+          <t>McCarthy and Stone</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -12943,25 +12923,25 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2009-04-16</t>
+          <t>2010-04-15</t>
         </is>
       </c>
       <c r="L153" t="b">
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>2</v>
+        <v>70.375</v>
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Lien 1</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>AIND-LYON</t>
+          <t>McCarthy-A06</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -12971,12 +12951,12 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=AIND-LYON</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=McCarthy-A06</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=AIND-LYON</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=McCarthy-A06</t>
         </is>
       </c>
       <c r="U153" t="inlineStr"/>
@@ -12986,37 +12966,43 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>McCarthy and Stone</t>
+          <t>Mediannuaire</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="b">
         <v>1</v>
       </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DC credit event determination (auction held)</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>9050</v>
+      </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2010-04-15</t>
+          <t>2013-01-31</t>
         </is>
       </c>
       <c r="L154" t="b">
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>70.375</v>
+        <v>40</v>
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
@@ -13027,22 +13013,22 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>McCarthy-A06</t>
+          <t>MEDIANA</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>creditfixings</t>
+          <t>dc-isda</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=McCarthy-A06</t>
+          <t>https://www.cdsdeterminationscommittees.org/lcds/mediannuaire-credit-event/</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=McCarthy-A06</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=MEDIANA</t>
         </is>
       </c>
       <c r="U154" t="inlineStr"/>
@@ -13052,43 +13038,37 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mediannuaire</t>
+          <t>Metro-Goldwyn-Mayer Inc.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="b">
         <v>1</v>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>DC credit event determination (auction held)</t>
-        </is>
-      </c>
-      <c r="G155" t="n">
-        <v>9050</v>
-      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2013-01-31</t>
+          <t>2009-11-10</t>
         </is>
       </c>
       <c r="L155" t="b">
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>40</v>
+        <v>58.5</v>
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
@@ -13099,22 +13079,22 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>MEDIANA</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>dc-isda</t>
+          <t>creditfixings</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>https://www.cdsdeterminationscommittees.org/lcds/mediannuaire-credit-event/</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=MGM</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=MEDIANA</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=MGM</t>
         </is>
       </c>
       <c r="U155" t="inlineStr"/>
@@ -13124,7 +13104,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Metro-Goldwyn-Mayer Inc.</t>
+          <t>National Joint Stock Company "Naftogaz of Ukraine"</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -13147,25 +13127,25 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2009-11-10</t>
+          <t>2009-12-16</t>
         </is>
       </c>
       <c r="L156" t="b">
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>58.5</v>
+        <v>83.5</v>
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Lien 1</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>NAFT</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13175,22 +13155,30 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=MGM</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=NAFT</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=MGM</t>
-        </is>
-      </c>
-      <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=NAFT</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Sovereign Restructuring Credit Event (19 Aug 2022) after creditors backed a two-year freeze on ~$20bn of debt amid the war; auction 28 Sep 2022. (Ukraine also had a 2015 Repudiation/Moratorium event.)</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>https://money.usnews.com/investing/news/articles/2022-08-19/ukraines-sovereign-debt-freeze-to-trigger-cds-payments</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>National Joint Stock Company "Naftogaz of Ukraine"</t>
+          <t>Pac Gas &amp; Elec Co</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -13213,14 +13201,14 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2009-12-16</t>
+          <t>2019-02-27</t>
         </is>
       </c>
       <c r="L157" t="b">
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>83.5</v>
+        <v>77.75</v>
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
@@ -13231,7 +13219,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>NAFT</t>
+          <t>PCG-PacGas+Elec</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13241,30 +13229,22 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=NAFT</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PCG-PacGas+Elec</t>
         </is>
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=NAFT</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>Sovereign Restructuring Credit Event (19 Aug 2022) after creditors backed a two-year freeze on ~$20bn of debt amid the war; auction 28 Sep 2022. (Ukraine also had a 2015 Repudiation/Moratorium event.)</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>https://money.usnews.com/investing/news/articles/2022-08-19/ukraines-sovereign-debt-freeze-to-trigger-cds-payments</t>
-        </is>
-      </c>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PCG-PacGas+Elec</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Pac Gas &amp; Elec Co</t>
+          <t>R.H. Donnelley Corporation</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -13287,14 +13267,14 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2019-02-27</t>
+          <t>2009-06-11</t>
         </is>
       </c>
       <c r="L158" t="b">
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>77.75</v>
+        <v>4.875</v>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
@@ -13305,7 +13285,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>PCG-PacGas+Elec</t>
+          <t>RHD</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13315,12 +13295,12 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PCG-PacGas+Elec</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD</t>
         </is>
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PCG-PacGas+Elec</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD</t>
         </is>
       </c>
       <c r="U158" t="inlineStr"/>
@@ -13330,7 +13310,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>R.H. Donnelley Corporation</t>
+          <t>R.H. Donnelley Inc.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -13353,25 +13333,25 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2009-06-11</t>
+          <t>2009-06-24</t>
         </is>
       </c>
       <c r="L159" t="b">
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>4.875</v>
+        <v>78.125</v>
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Lien 1</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>RHD</t>
+          <t>RHD-Inc</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -13381,12 +13361,12 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD-Inc</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD-Inc</t>
         </is>
       </c>
       <c r="U159" t="inlineStr"/>
@@ -13396,7 +13376,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>R.H. Donnelley Inc.</t>
+          <t>Six Flags Theme Parks Inc.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -13419,14 +13399,14 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2009-06-24</t>
+          <t>2009-07-09</t>
         </is>
       </c>
       <c r="L160" t="b">
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>78.125</v>
+        <v>96.125</v>
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
@@ -13437,7 +13417,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>RHD-Inc</t>
+          <t>PKS-SFTP</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -13447,12 +13427,12 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD-Inc</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS-SFTP</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=RHD-Inc</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS-SFTP</t>
         </is>
       </c>
       <c r="U160" t="inlineStr"/>
@@ -13462,7 +13442,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Six Flags Theme Parks Inc.</t>
+          <t>Six Flags, Inc.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -13492,18 +13472,18 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>96.125</v>
+        <v>14</v>
       </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Lien 1</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>PKS-SFTP</t>
+          <t>PKS</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -13513,12 +13493,12 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS-SFTP</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS-SFTP</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS</t>
         </is>
       </c>
       <c r="U161" t="inlineStr"/>
@@ -13528,7 +13508,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Six Flags, Inc.</t>
+          <t>SSP Financing Limited</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -13551,25 +13531,25 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2009-07-09</t>
+          <t>2009-10-08</t>
         </is>
       </c>
       <c r="L162" t="b">
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>14</v>
+        <v>52.375</v>
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Lien 1</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>PKS</t>
+          <t>SSPFIN</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -13579,12 +13559,12 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SSPFIN</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=PKS</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SSPFIN</t>
         </is>
       </c>
       <c r="U162" t="inlineStr"/>
@@ -13594,7 +13574,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SSP Financing Limited</t>
+          <t>Syncora Guarantee Inc.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -13617,25 +13597,25 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2009-10-08</t>
+          <t>2009-05-27</t>
         </is>
       </c>
       <c r="L163" t="b">
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>52.375</v>
+        <v>15</v>
       </c>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Lien 1</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>SSPFIN</t>
+          <t>SYNHL-Gua</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -13645,12 +13625,12 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SSPFIN</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SYNHL-Gua</t>
         </is>
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SSPFIN</t>
+          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SYNHL-Gua</t>
         </is>
       </c>
       <c r="U163" t="inlineStr"/>
@@ -13660,37 +13640,51 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Syncora Guarantee Inc.</t>
+          <t>Takefuji Corporation</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
       <c r="E164" t="b">
         <v>1</v>
       </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>DC credit event determination (auction held)</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2010092801</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2009-05-27</t>
+          <t>2010-10-28</t>
         </is>
       </c>
       <c r="L164" t="b">
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
@@ -13701,22 +13695,22 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>SYNHL-Gua</t>
+          <t>TAKFUJ</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>creditfixings</t>
+          <t>dc-isda</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SYNHL-Gua</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/takefuji-corporation/</t>
         </is>
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>https://www.creditfixings.com/CreditEventAuctions/results.jsp?ticker=SYNHL-Gua</t>
+          <t>https://www.cdsdeterminationscommittees.org/cds/takefuji-corporation/</t>
         </is>
       </c>
       <c r="U164" t="inlineStr"/>
